--- a/dados/ES.xlsx
+++ b/dados/ES.xlsx
@@ -82,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -115,6 +115,9 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -192,7 +195,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_ES" displayName="Tabela_ES" ref="A1:X504" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_ES" displayName="Tabela_ES" ref="A1:X518" headerRowCount="1">
   <autoFilter ref="A1:X504"/>
   <tableColumns count="24">
     <tableColumn id="1" name="ID"/>
@@ -489,7 +492,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X504"/>
+  <dimension ref="A1:X518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" customWidth="1" min="1" max="1"/>
@@ -52526,6 +52529,1392 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>ES21</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>ES-VILA_VELHA 1</t>
+        </is>
+      </c>
+      <c r="D505" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E505" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F505" s="13" t="n">
+        <v>1427.519</v>
+      </c>
+      <c r="G505" s="13" t="n">
+        <v>29414.75</v>
+      </c>
+      <c r="H505" s="13" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>BBK7A74</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GEORGE SANTANA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K505" s="14" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:24 BRT</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:44 BRT</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V505" s="9">
+        <f>IFERROR(F505/H505,"")</f>
+        <v/>
+      </c>
+      <c r="W505" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>ES4</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>RGB(0,0,255)</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>ES-ARACRUZ</t>
+        </is>
+      </c>
+      <c r="D506" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E506" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F506" s="13" t="n">
+        <v>691.3713</v>
+      </c>
+      <c r="G506" s="13" t="n">
+        <v>16757.533</v>
+      </c>
+      <c r="H506" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>EMG8E81</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, WAGNER GOMES PEIXOTO</t>
+        </is>
+      </c>
+      <c r="K506" s="14" t="n">
+        <v>262.9</v>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:23 BRT</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V506" s="9">
+        <f>IFERROR(F506/H506,"")</f>
+        <v/>
+      </c>
+      <c r="W506" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>ES9</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>RGB(128,0,128)</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>ES-SAO_MATEUS</t>
+        </is>
+      </c>
+      <c r="D507" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E507" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="F507" s="13" t="n">
+        <v>1260.653</v>
+      </c>
+      <c r="G507" s="13" t="n">
+        <v>23746.417</v>
+      </c>
+      <c r="H507" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>JIU0I59</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MAYCON CAITANO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K507" s="14" t="n">
+        <v>585.41</v>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:23 BRT</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V507" s="9">
+        <f>IFERROR(F507/H507,"")</f>
+        <v/>
+      </c>
+      <c r="W507" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>ES18</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>ES-GUARAPARI</t>
+        </is>
+      </c>
+      <c r="D508" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="E508" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F508" s="13" t="n">
+        <v>1145.6937</v>
+      </c>
+      <c r="G508" s="13" t="n">
+        <v>18680.04</v>
+      </c>
+      <c r="H508" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>ODC0A49</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, EDER HENRIQUE HARCKBART</t>
+        </is>
+      </c>
+      <c r="K508" s="14" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:44 BRT</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V508" s="9">
+        <f>IFERROR(F508/H508,"")</f>
+        <v/>
+      </c>
+      <c r="W508" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>ES22</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>RGB(128,128,128)</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>ES-CARIACICA</t>
+        </is>
+      </c>
+      <c r="D509" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E509" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F509" s="13" t="n">
+        <v>1958.679</v>
+      </c>
+      <c r="G509" s="13" t="n">
+        <v>91670.11</v>
+      </c>
+      <c r="H509" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>OZG5D14</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ELIAS MARQUES SANTOS</t>
+        </is>
+      </c>
+      <c r="K509" s="14" t="n">
+        <v>78.23</v>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:44 BRT</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V509" s="9">
+        <f>IFERROR(F509/H509,"")</f>
+        <v/>
+      </c>
+      <c r="W509" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>ES20</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>RGB(255,0,0)</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>ES-VITORIA</t>
+        </is>
+      </c>
+      <c r="D510" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E510" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F510" s="13" t="n">
+        <v>640.4896</v>
+      </c>
+      <c r="G510" s="13" t="n">
+        <v>16086.12</v>
+      </c>
+      <c r="H510" s="13" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>QIL8C32</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GIANI OLIVEIRI SILVA MENEZES</t>
+        </is>
+      </c>
+      <c r="K510" s="14" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:44 BRT</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V510" s="9">
+        <f>IFERROR(F510/H510,"")</f>
+        <v/>
+      </c>
+      <c r="W510" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>ES23</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>ES-VILA_VELHA 2</t>
+        </is>
+      </c>
+      <c r="D511" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E511" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F511" s="13" t="n">
+        <v>3556.188</v>
+      </c>
+      <c r="G511" s="13" t="n">
+        <v>29635.31</v>
+      </c>
+      <c r="H511" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>QRE0B98</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, JORGE SANTOS DE ALMEIDA JUNIOR</t>
+        </is>
+      </c>
+      <c r="K511" s="14" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:23 BRT</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:44 BRT</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V511" s="9">
+        <f>IFERROR(F511/H511,"")</f>
+        <v/>
+      </c>
+      <c r="W511" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>ES19</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>ES-SERRA</t>
+        </is>
+      </c>
+      <c r="D512" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E512" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F512" s="13" t="n">
+        <v>689.0575</v>
+      </c>
+      <c r="G512" s="13" t="n">
+        <v>14188.174</v>
+      </c>
+      <c r="H512" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>RDN7A43</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, CRISTIANO PENA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K512" s="14" t="n">
+        <v>183.56</v>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:44 BRT</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V512" s="9">
+        <f>IFERROR(F512/H512,"")</f>
+        <v/>
+      </c>
+      <c r="W512" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>ES16</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>ES-CACHOEIRO_ITAPEMIRIM</t>
+        </is>
+      </c>
+      <c r="D513" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E513" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F513" s="13" t="n">
+        <v>1961.9199</v>
+      </c>
+      <c r="G513" s="13" t="n">
+        <v>35506.45</v>
+      </c>
+      <c r="H513" s="13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>RYY6A10</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GIDEVALDO DE AVELAR CONCEICAO</t>
+        </is>
+      </c>
+      <c r="K513" s="14" t="n">
+        <v>388.01</v>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:44 BRT</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V513" s="9">
+        <f>IFERROR(F513/H513,"")</f>
+        <v/>
+      </c>
+      <c r="W513" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>ES12</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>RGB(218,165,32)</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>ES-PEDRO_CANARIO-BARRA</t>
+        </is>
+      </c>
+      <c r="D514" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E514" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="F514" s="13" t="n">
+        <v>1291.4517</v>
+      </c>
+      <c r="G514" s="13" t="n">
+        <v>23275.11</v>
+      </c>
+      <c r="H514" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>SXK7D10</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GEREMIAS QUIRINO DE JESUS</t>
+        </is>
+      </c>
+      <c r="K514" s="14" t="n">
+        <v>766.46</v>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:23 BRT</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V514" s="9">
+        <f>IFERROR(F514/H514,"")</f>
+        <v/>
+      </c>
+      <c r="W514" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>ES14</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>RGB(238,130,238)</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>ES-MARATAIZES</t>
+        </is>
+      </c>
+      <c r="D515" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E515" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="F515" s="13" t="n">
+        <v>1074.8027</v>
+      </c>
+      <c r="G515" s="13" t="n">
+        <v>14568.922</v>
+      </c>
+      <c r="H515" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>SXN7J08</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ALISSON NERES SANTANA</t>
+        </is>
+      </c>
+      <c r="K515" s="14" t="n">
+        <v>263.83</v>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:44 BRT</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V515" s="9">
+        <f>IFERROR(F515/H515,"")</f>
+        <v/>
+      </c>
+      <c r="W515" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>RGB(160,82,45)</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>ES-SAO_GABRIEL-VALERIO</t>
+        </is>
+      </c>
+      <c r="D516" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="E516" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F516" s="13" t="n">
+        <v>885.1463</v>
+      </c>
+      <c r="G516" s="13" t="n">
+        <v>23327.76</v>
+      </c>
+      <c r="H516" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>SXN8A08</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, RENILDO CARLOS PEREIRA</t>
+        </is>
+      </c>
+      <c r="K516" s="14" t="n">
+        <v>385.72</v>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:23 BRT</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V516" s="9">
+        <f>IFERROR(F516/H516,"")</f>
+        <v/>
+      </c>
+      <c r="W516" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>ES1</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>ES-LINHARES</t>
+        </is>
+      </c>
+      <c r="D517" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="E517" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="F517" s="13" t="n">
+        <v>1828.3409</v>
+      </c>
+      <c r="G517" s="13" t="n">
+        <v>42125.13</v>
+      </c>
+      <c r="H517" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>SXN8A48</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ADEMILSON CORREIA DA SILVA</t>
+        </is>
+      </c>
+      <c r="K517" s="14" t="n">
+        <v>437.03</v>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>19/08/2026 19:20 BRT</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>19/08/2026 18:23 BRT</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>21/08/2026 - ROTERIZAÇÃO - SEXTA</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V517" s="9">
+        <f>IFERROR(F517/H517,"")</f>
+        <v/>
+      </c>
+      <c r="W517" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D518" s="12" t="n">
+        <v>286</v>
+      </c>
+      <c r="E518" s="12" t="n">
+        <v>405</v>
+      </c>
+      <c r="F518" s="13" t="n">
+        <v>18411.3126</v>
+      </c>
+      <c r="G518" s="13" t="n">
+        <v>378981.826</v>
+      </c>
+      <c r="H518" s="13" t="n">
+        <v>41600</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K518" s="14" t="n">
+        <v>3812.21</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V518" s="9">
+        <f>IFERROR(F518/H518,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/dados/ES.xlsx
+++ b/dados/ES.xlsx
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_ES" displayName="Tabela_ES" ref="A1:X572" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_ES" displayName="Tabela_ES" ref="A1:X595" headerRowCount="1">
   <autoFilter ref="A1:X553"/>
   <tableColumns count="24">
     <tableColumn id="1" name="ID"/>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X572"/>
+  <dimension ref="A1:X595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" customWidth="1" min="1" max="1"/>
@@ -59495,6 +59495,2288 @@
         <v/>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>ESLINHARES2</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>RGB(0,255,255)</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>ES-LINHARES2</t>
+        </is>
+      </c>
+      <c r="D573" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E573" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F573" s="13" t="n">
+        <v>5539.5131</v>
+      </c>
+      <c r="G573" s="13" t="n">
+        <v>160521.03</v>
+      </c>
+      <c r="H573" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>PJQ3D71</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, SERGIO ALVES DA SILVA</t>
+        </is>
+      </c>
+      <c r="K573" s="14" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:10 BRT</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:51 BRT</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V573" s="9">
+        <f>IFERROR(F573/H573,"")</f>
+        <v/>
+      </c>
+      <c r="W573" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>RGB(147,112,219)</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>ES-VILA VELHA 2</t>
+        </is>
+      </c>
+      <c r="D574" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E574" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F574" s="13" t="n">
+        <v>4079.7615</v>
+      </c>
+      <c r="G574" s="13" t="n">
+        <v>31398.425</v>
+      </c>
+      <c r="H574" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>QRE0B98</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GIANI OLIVEIRI SILVA MENEZES</t>
+        </is>
+      </c>
+      <c r="K574" s="14" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:10 BRT</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:07 BRT</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V574" s="9">
+        <f>IFERROR(F574/H574,"")</f>
+        <v/>
+      </c>
+      <c r="W574" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>ES3</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>RGB(255,140,0)</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>ES-RIO_BANANAL</t>
+        </is>
+      </c>
+      <c r="D575" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="E575" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="F575" s="13" t="n">
+        <v>1012.9851</v>
+      </c>
+      <c r="G575" s="13" t="n">
+        <v>23385.6</v>
+      </c>
+      <c r="H575" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>JIU0I59</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MAYCON CAITANO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K575" s="14" t="n">
+        <v>153</v>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:48 BRT</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V575" s="9">
+        <f>IFERROR(F575/H575,"")</f>
+        <v/>
+      </c>
+      <c r="W575" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>ES4</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>RGB(0,0,255)</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>ES-COLATINA-SAO_ROQUE</t>
+        </is>
+      </c>
+      <c r="D576" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E576" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F576" s="13" t="n">
+        <v>623.4723</v>
+      </c>
+      <c r="G576" s="13" t="n">
+        <v>14606.385</v>
+      </c>
+      <c r="H576" s="13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>TPX3G84</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, VITORIO BATISTA DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="K576" s="14" t="n">
+        <v>366.72</v>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:48 BRT</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V576" s="9">
+        <f>IFERROR(F576/H576,"")</f>
+        <v/>
+      </c>
+      <c r="W576" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>ES19</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>ES-SERRA</t>
+        </is>
+      </c>
+      <c r="D577" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E577" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F577" s="13" t="n">
+        <v>728.9566</v>
+      </c>
+      <c r="G577" s="13" t="n">
+        <v>15181.998</v>
+      </c>
+      <c r="H577" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>RDN7A43</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, CRISTIANO PENA OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K577" s="14" t="n">
+        <v>102.37</v>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V577" s="9">
+        <f>IFERROR(F577/H577,"")</f>
+        <v/>
+      </c>
+      <c r="W577" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>ES5</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>RGB(255,105,180)</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>ES-SAO_GABRIEL-VALERIO</t>
+        </is>
+      </c>
+      <c r="D578" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E578" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F578" s="13" t="n">
+        <v>848.131</v>
+      </c>
+      <c r="G578" s="13" t="n">
+        <v>17972.1</v>
+      </c>
+      <c r="H578" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>SXN8A08</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, RENILDO CARLOS PEREIRA</t>
+        </is>
+      </c>
+      <c r="K578" s="14" t="n">
+        <v>266.02</v>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:48 BRT</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V578" s="9">
+        <f>IFERROR(F578/H578,"")</f>
+        <v/>
+      </c>
+      <c r="W578" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>ES15</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>RGB(210,105,30)</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>ES-PINHEIROS</t>
+        </is>
+      </c>
+      <c r="D579" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E579" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F579" s="13" t="n">
+        <v>834.1739</v>
+      </c>
+      <c r="G579" s="13" t="n">
+        <v>19110.59</v>
+      </c>
+      <c r="H579" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>EMG8E81</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, WAGNER GOMES PEIXOTO</t>
+        </is>
+      </c>
+      <c r="K579" s="14" t="n">
+        <v>419.71</v>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:48 BRT</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V579" s="9">
+        <f>IFERROR(F579/H579,"")</f>
+        <v/>
+      </c>
+      <c r="W579" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>ES16</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>ES-VILA_VELHA</t>
+        </is>
+      </c>
+      <c r="D580" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E580" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F580" s="13" t="n">
+        <v>729.2255</v>
+      </c>
+      <c r="G580" s="13" t="n">
+        <v>16438.854</v>
+      </c>
+      <c r="H580" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>ODC0A49</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, EDER HENRIQUE HARCKBART</t>
+        </is>
+      </c>
+      <c r="K580" s="14" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V580" s="9">
+        <f>IFERROR(F580/H580,"")</f>
+        <v/>
+      </c>
+      <c r="W580" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>ES26</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>ES-CACHOEIRO_ITAPEMIRIM</t>
+        </is>
+      </c>
+      <c r="D581" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E581" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F581" s="13" t="n">
+        <v>1473.9435</v>
+      </c>
+      <c r="G581" s="13" t="n">
+        <v>18434.735</v>
+      </c>
+      <c r="H581" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>PWQ5C35</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, VALMIRO DE OLIVEIRA NASCENTE</t>
+        </is>
+      </c>
+      <c r="K581" s="14" t="n">
+        <v>316.54</v>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V581" s="9">
+        <f>IFERROR(F581/H581,"")</f>
+        <v/>
+      </c>
+      <c r="W581" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X581" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>ES2</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>ES-LINHARES</t>
+        </is>
+      </c>
+      <c r="D582" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="E582" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="F582" s="13" t="n">
+        <v>1623.9622</v>
+      </c>
+      <c r="G582" s="13" t="n">
+        <v>29709.708</v>
+      </c>
+      <c r="H582" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>SXN8A48</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ADEMILSON CORREIA DA SILVA</t>
+        </is>
+      </c>
+      <c r="K582" s="14" t="n">
+        <v>70.73</v>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:48 BRT</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V582" s="9">
+        <f>IFERROR(F582/H582,"")</f>
+        <v/>
+      </c>
+      <c r="W582" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X582" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>ES29</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>RGB(128,128,128)</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>ES-MUQUI_MIMOSO</t>
+        </is>
+      </c>
+      <c r="D583" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E583" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F583" s="13" t="n">
+        <v>954.4279</v>
+      </c>
+      <c r="G583" s="13" t="n">
+        <v>16730.79</v>
+      </c>
+      <c r="H583" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>NZR4F11</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ALESSANDRO SANTOS FARIAS</t>
+        </is>
+      </c>
+      <c r="K583" s="14" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V583" s="9">
+        <f>IFERROR(F583/H583,"")</f>
+        <v/>
+      </c>
+      <c r="W583" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X583" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>ES17</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>RGB(128,128,128)</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>ES-CARIACICA</t>
+        </is>
+      </c>
+      <c r="D584" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E584" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="F584" s="13" t="n">
+        <v>1063.9582</v>
+      </c>
+      <c r="G584" s="13" t="n">
+        <v>18857.054</v>
+      </c>
+      <c r="H584" s="13" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>BBK7A74</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ELIAS MARQUES SANTOS</t>
+        </is>
+      </c>
+      <c r="K584" s="14" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V584" s="9">
+        <f>IFERROR(F584/H584,"")</f>
+        <v/>
+      </c>
+      <c r="W584" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X584" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>ES23</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>RGB(238,130,238)</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>ES-MARATAIZES</t>
+        </is>
+      </c>
+      <c r="D585" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E585" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F585" s="13" t="n">
+        <v>1474.227</v>
+      </c>
+      <c r="G585" s="13" t="n">
+        <v>24738.528</v>
+      </c>
+      <c r="H585" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>SXN7J08</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, JORGE SANTOS DE ALMEIDA JUNIOR</t>
+        </is>
+      </c>
+      <c r="K585" s="14" t="n">
+        <v>265.29</v>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V585" s="9">
+        <f>IFERROR(F585/H585,"")</f>
+        <v/>
+      </c>
+      <c r="W585" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X585" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>ES18</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>RGB(255,0,0)</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>ES-VITORIA</t>
+        </is>
+      </c>
+      <c r="D586" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E586" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F586" s="13" t="n">
+        <v>927.6607</v>
+      </c>
+      <c r="G586" s="13" t="n">
+        <v>22378.04</v>
+      </c>
+      <c r="H586" s="13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>RYY6A10</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, KEWEN CANDOTE HERINGER</t>
+        </is>
+      </c>
+      <c r="K586" s="14" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>26/08/2026 06:49 BRT</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEWEN CANDOTE HERINGER </t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V586" s="9">
+        <f>IFERROR(F586/H586,"")</f>
+        <v/>
+      </c>
+      <c r="W586" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X586" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>ES20</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>ES-GUARAPARI</t>
+        </is>
+      </c>
+      <c r="D587" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E587" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F587" s="13" t="n">
+        <v>1078.6405</v>
+      </c>
+      <c r="G587" s="13" t="n">
+        <v>19364.64</v>
+      </c>
+      <c r="H587" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>OZG5D14</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GEORGE SANTANA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K587" s="14" t="n">
+        <v>153.99</v>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V587" s="9">
+        <f>IFERROR(F587/H587,"")</f>
+        <v/>
+      </c>
+      <c r="W587" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X587" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>ES28</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>RGB(128,0,128)</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>ES-ALEGRE-GUACUI</t>
+        </is>
+      </c>
+      <c r="D588" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E588" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F588" s="13" t="n">
+        <v>1076.7977</v>
+      </c>
+      <c r="G588" s="13" t="n">
+        <v>20644.51</v>
+      </c>
+      <c r="H588" s="13" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>ODD8C33</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, WERLISON SANTOS SILVA</t>
+        </is>
+      </c>
+      <c r="K588" s="14" t="n">
+        <v>457.78</v>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V588" s="9">
+        <f>IFERROR(F588/H588,"")</f>
+        <v/>
+      </c>
+      <c r="W588" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X588" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>ES10</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>RGB(32,178,170)</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>ES-BARRA_SAO_FRANCISCO</t>
+        </is>
+      </c>
+      <c r="D589" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E589" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F589" s="13" t="n">
+        <v>1461.118</v>
+      </c>
+      <c r="G589" s="13" t="n">
+        <v>25951.93</v>
+      </c>
+      <c r="H589" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>SXK7D20</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, RANDERSON JESUS DA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="K589" s="14" t="n">
+        <v>486.83</v>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:48 BRT</t>
+        </is>
+      </c>
+      <c r="Q589" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V589" s="9">
+        <f>IFERROR(F589/H589,"")</f>
+        <v/>
+      </c>
+      <c r="W589" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X589" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>ES25</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>RGB(0,0,255)</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>ES-VARGEM_ALTA - DOMINGOS M - BR262</t>
+        </is>
+      </c>
+      <c r="D590" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E590" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F590" s="13" t="n">
+        <v>1349.8418</v>
+      </c>
+      <c r="G590" s="13" t="n">
+        <v>38032.77</v>
+      </c>
+      <c r="H590" s="13" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>OYK3D99</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MANOEL ELISANDRO DA SILVA</t>
+        </is>
+      </c>
+      <c r="K590" s="14" t="n">
+        <v>443.18</v>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V590" s="9">
+        <f>IFERROR(F590/H590,"")</f>
+        <v/>
+      </c>
+      <c r="W590" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>ES9</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>RGB(128,0,128)</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>ES-PANCAS</t>
+        </is>
+      </c>
+      <c r="D591" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E591" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F591" s="13" t="n">
+        <v>1224.1203</v>
+      </c>
+      <c r="G591" s="13" t="n">
+        <v>23252.605</v>
+      </c>
+      <c r="H591" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>MTW4J36</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, THIAGO KOSKI SEPULCHRO</t>
+        </is>
+      </c>
+      <c r="K591" s="14" t="n">
+        <v>419.1</v>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:48 BRT</t>
+        </is>
+      </c>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>VAN-II</t>
+        </is>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V591" s="9">
+        <f>IFERROR(F591/H591,"")</f>
+        <v/>
+      </c>
+      <c r="W591" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>RGB(160,82,45)</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>ES-STA_TEREZA-STA_MARIA</t>
+        </is>
+      </c>
+      <c r="D592" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="E592" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="F592" s="13" t="n">
+        <v>1678.9567</v>
+      </c>
+      <c r="G592" s="13" t="n">
+        <v>34856.952</v>
+      </c>
+      <c r="H592" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>SXN7C48</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, DIRCEU DUTRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K592" s="14" t="n">
+        <v>450.09</v>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:48 BRT</t>
+        </is>
+      </c>
+      <c r="Q592" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V592" s="9">
+        <f>IFERROR(F592/H592,"")</f>
+        <v/>
+      </c>
+      <c r="W592" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>ES12</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>RGB(218,165,32)</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>ES-NOVA_VENECIA</t>
+        </is>
+      </c>
+      <c r="D593" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="E593" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F593" s="13" t="n">
+        <v>1631.7448</v>
+      </c>
+      <c r="G593" s="13" t="n">
+        <v>38680.25</v>
+      </c>
+      <c r="H593" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>SXK7C60</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, MURILO MARINHO VIEIRA</t>
+        </is>
+      </c>
+      <c r="K593" s="14" t="n">
+        <v>396.32</v>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:48 BRT</t>
+        </is>
+      </c>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>3/4-III</t>
+        </is>
+      </c>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V593" s="9">
+        <f>IFERROR(F593/H593,"")</f>
+        <v/>
+      </c>
+      <c r="W593" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>ES27</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>RGB(255,215,0)</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>ES-MUNIZ_FREIRE</t>
+        </is>
+      </c>
+      <c r="D594" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="E594" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F594" s="13" t="n">
+        <v>1914.99</v>
+      </c>
+      <c r="G594" s="13" t="n">
+        <v>30658.816</v>
+      </c>
+      <c r="H594" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>PPB2D54</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ELIELSON RIBEIRO LUXINGER</t>
+        </is>
+      </c>
+      <c r="K594" s="14" t="n">
+        <v>596.79</v>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>WESLEY, JONH</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:09 BRT</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:05 BRT</t>
+        </is>
+      </c>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>d9098jo@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>3/4-IV</t>
+        </is>
+      </c>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>27/08/2026 - ROTERIZAÇÃO - QUINTA - 27/08/2026</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V594" s="9">
+        <f>IFERROR(F594/H594,"")</f>
+        <v/>
+      </c>
+      <c r="W594" t="inlineStr">
+        <is>
+          <t>27/08</t>
+        </is>
+      </c>
+      <c r="X594" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D595" s="12" t="n">
+        <v>497</v>
+      </c>
+      <c r="E595" s="12" t="n">
+        <v>739</v>
+      </c>
+      <c r="F595" s="13" t="n">
+        <v>33330.6083</v>
+      </c>
+      <c r="G595" s="13" t="n">
+        <v>660906.3100000001</v>
+      </c>
+      <c r="H595" s="13" t="n">
+        <v>68900</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K595" s="14" t="n">
+        <v>6058.21</v>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V595" s="9">
+        <f>IFERROR(F595/H595,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
